--- a/Data/Skill.xlsx
+++ b/Data/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDAD7F1-54DA-4215-91C8-380C1561A7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5437B53-1F90-4D9F-98EB-200E79755316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="2430" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActiveSkill" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="37">
   <si>
     <t>SkillId</t>
   </si>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>ResourceIndex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_dash</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -175,7 +179,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +190,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -201,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -209,6 +219,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -617,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="K2" s="2">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="L2" s="2">
         <v>0.1</v>
@@ -649,10 +663,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -668,16 +682,16 @@
         <v>10</v>
       </c>
       <c r="J3" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="L3" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="M3" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N3" t="s">
         <v>34</v>
@@ -686,10 +700,10 @@
         <v>180</v>
       </c>
       <c r="P3" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2">
         <v>3</v>
@@ -779,7 +793,7 @@
         <v>6</v>
       </c>
       <c r="K5" s="2">
-        <v>1.6</v>
+        <v>0.25</v>
       </c>
       <c r="L5" s="2">
         <v>0.11</v>
@@ -803,58 +817,58 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>1005</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="4">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="2">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="F6" s="3">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="3">
         <v>12</v>
       </c>
-      <c r="K6" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="K6" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="L6" s="3">
         <v>0.16</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="3">
         <v>6</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" s="2">
+        <v>33</v>
+      </c>
+      <c r="O6" s="3">
         <v>270</v>
       </c>
-      <c r="P6" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>1</v>
-      </c>
-      <c r="R6" s="2">
-        <v>1.5</v>
+      <c r="P6" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>10</v>
+      </c>
+      <c r="R6" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -887,7 +901,7 @@
         <v>10</v>
       </c>
       <c r="K7" s="2">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="L7" s="2">
         <v>0.18</v>
@@ -941,7 +955,7 @@
         <v>12</v>
       </c>
       <c r="K8" s="2">
-        <v>2.2999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="L8" s="2">
         <v>0.17</v>
@@ -995,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="K9" s="2">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="2">
         <v>0.2</v>
@@ -1049,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="K10" s="2">
-        <v>2.7</v>
+        <v>0.23</v>
       </c>
       <c r="L10" s="2">
         <v>0.19</v>
@@ -1073,58 +1087,58 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
         <v>1010</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="D11" s="4">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
         <v>25</v>
       </c>
-      <c r="G11" s="2">
-        <v>5</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
+      <c r="G11" s="3">
+        <v>5</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="3">
         <v>15</v>
       </c>
-      <c r="K11" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="L11" s="2">
+      <c r="K11" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L11" s="3">
         <v>0.19</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="3">
         <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O11" s="2">
+        <v>33</v>
+      </c>
+      <c r="O11" s="3">
         <v>270</v>
       </c>
-      <c r="P11" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2">
-        <v>3</v>
+      <c r="P11" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>10</v>
+      </c>
+      <c r="R11" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -1157,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="K12" s="2">
-        <v>3.5</v>
+        <v>0.15</v>
       </c>
       <c r="L12" s="2">
         <v>0.25</v>
@@ -1211,7 +1225,7 @@
         <v>18</v>
       </c>
       <c r="K13" s="2">
-        <v>4</v>
+        <v>0.11</v>
       </c>
       <c r="L13" s="2">
         <v>0.3</v>
@@ -1265,7 +1279,7 @@
         <v>18</v>
       </c>
       <c r="K14" s="2">
-        <v>3.8</v>
+        <v>0.42</v>
       </c>
       <c r="L14" s="2">
         <v>0.28000000000000003</v>
@@ -1319,7 +1333,7 @@
         <v>14</v>
       </c>
       <c r="K15" s="2">
-        <v>3.6</v>
+        <v>0.18</v>
       </c>
       <c r="L15" s="2">
         <v>0.26</v>
@@ -1343,57 +1357,57 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+    <row r="16" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
         <v>1015</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16" s="2">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="D16" s="4">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3">
         <v>40</v>
       </c>
-      <c r="G16" s="2">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="G16" s="3">
+        <v>5</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="3">
         <v>20</v>
       </c>
-      <c r="K16" s="2">
-        <v>4.2</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="K16" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L16" s="3">
         <v>0.32</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="3">
         <v>11</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" s="3">
         <v>270</v>
       </c>
-      <c r="P16" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>2</v>
-      </c>
-      <c r="R16" s="2">
+      <c r="P16" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>10</v>
+      </c>
+      <c r="R16" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1427,7 +1441,7 @@
         <v>16</v>
       </c>
       <c r="K17" s="2">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="L17" s="2">
         <v>0.35</v>
@@ -1481,7 +1495,7 @@
         <v>20</v>
       </c>
       <c r="K18" s="2">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="L18" s="2">
         <v>0.33</v>
@@ -1535,7 +1549,7 @@
         <v>22</v>
       </c>
       <c r="K19" s="2">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="L19" s="2">
         <v>0.4</v>
@@ -1589,7 +1603,7 @@
         <v>18</v>
       </c>
       <c r="K20" s="2">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="L20" s="2">
         <v>0.38</v>
@@ -1613,57 +1627,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+    <row r="21" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
         <v>1020</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D21">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D21" s="4">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3">
         <v>4</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>55</v>
       </c>
-      <c r="G21" s="2">
-        <v>5</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="G21" s="3">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3">
         <v>25</v>
       </c>
-      <c r="K21" s="2">
-        <v>5.2</v>
-      </c>
-      <c r="L21" s="2">
+      <c r="K21" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L21" s="3">
         <v>0.42</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="3">
         <v>14</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="3">
         <v>270</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="3">
         <v>1.8</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="3">
         <v>4</v>
       </c>
-      <c r="R21" s="2">
+      <c r="R21" s="3">
         <v>1.8</v>
       </c>
     </row>
@@ -1697,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="K22" s="2">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="2">
         <v>0.45</v>
@@ -1751,7 +1765,7 @@
         <v>25</v>
       </c>
       <c r="K23" s="2">
-        <v>5.3</v>
+        <v>0.2</v>
       </c>
       <c r="L23" s="2">
         <v>0.43</v>
@@ -1805,7 +1819,7 @@
         <v>30</v>
       </c>
       <c r="K24" s="2">
-        <v>6</v>
+        <v>0.23</v>
       </c>
       <c r="L24" s="2">
         <v>0.5</v>
@@ -1859,7 +1873,7 @@
         <v>24</v>
       </c>
       <c r="K25" s="2">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="2">
         <v>0.48</v>
@@ -1883,57 +1897,57 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+    <row r="26" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
         <v>1025</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D26">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2">
-        <v>5</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="D26" s="4">
+        <v>9</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
         <v>70</v>
       </c>
-      <c r="G26" s="2">
-        <v>5</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="G26" s="3">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="3">
         <v>35</v>
       </c>
-      <c r="K26" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="L26" s="2">
+      <c r="K26" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="L26" s="3">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="3">
         <v>20</v>
       </c>
-      <c r="N26" t="s">
+      <c r="N26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O26" s="2">
+      <c r="O26" s="3">
         <v>270</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="3">
         <v>1.5</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="3">
         <v>1</v>
       </c>
-      <c r="R26" s="2">
+      <c r="R26" s="3">
         <v>1.5</v>
       </c>
     </row>

--- a/Data/Skill.xlsx
+++ b/Data/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5437B53-1F90-4D9F-98EB-200E79755316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46AF504-E352-4BE0-B945-191C9AE11B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2910" yWindow="3435" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActiveSkill" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="40">
   <si>
     <t>SkillId</t>
   </si>
@@ -148,6 +148,18 @@
   </si>
   <si>
     <t>Skill_dash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActorType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lantern</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -179,7 +191,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,6 +210,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -211,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -223,6 +253,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -525,97 +565,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="K1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -623,138 +666,144 @@
       <c r="G2" s="2">
         <v>1</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="2">
-        <v>5</v>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="K2" s="2">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2">
         <v>0.6</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>0.1</v>
       </c>
-      <c r="M2" s="2">
-        <v>3</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2">
-        <v>-1</v>
-      </c>
       <c r="P2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q2" s="2">
         <v>1.5</v>
       </c>
-      <c r="Q2" s="2">
-        <v>5</v>
-      </c>
       <c r="R2" s="2">
+        <v>5</v>
+      </c>
+      <c r="S2" s="2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>36</v>
       </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
+      <c r="E3">
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="K3" s="2">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2">
         <v>0.8</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>0.1</v>
       </c>
-      <c r="M3" s="2">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="N3" s="2">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>180</v>
       </c>
-      <c r="P3" s="2">
-        <v>5</v>
-      </c>
       <c r="Q3" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R3" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1003</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>7</v>
       </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
       <c r="F4" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="2">
-        <v>10</v>
-      </c>
       <c r="K4" s="2">
+        <v>10</v>
+      </c>
+      <c r="L4" s="2">
         <v>1.8</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>0.12</v>
       </c>
-      <c r="M4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="2">
-        <v>-1</v>
-      </c>
       <c r="P4" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q4" s="2">
         <v>2</v>
@@ -762,1221 +811,1290 @@
       <c r="R4" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1004</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>8</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
       <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
         <v>8</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>4</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2">
         <v>6</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>0.25</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>0.11</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <v>4</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="2">
-        <v>-1</v>
-      </c>
       <c r="P5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q5" s="2">
         <v>1.8</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>8</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>1.8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1005</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
+      <c r="E6" s="4">
+        <v>9</v>
       </c>
       <c r="F6" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3">
         <v>12</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>0.3</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>0.16</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>6</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>270</v>
       </c>
-      <c r="P6" s="3">
-        <v>3</v>
-      </c>
       <c r="Q6" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R6" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="S6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1006</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
+      <c r="E7">
+        <v>5</v>
       </c>
       <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
         <v>15</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="2">
+        <v>10</v>
+      </c>
+      <c r="L7" s="2">
         <v>0.2</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>0.18</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>7</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="2">
-        <v>-1</v>
-      </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="S7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1007</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>6</v>
       </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
       <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
         <v>18</v>
       </c>
-      <c r="G8" s="2">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>12</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <v>0.8</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>0.17</v>
       </c>
-      <c r="M8" s="2">
-        <v>2</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="N8" s="2">
+        <v>2</v>
+      </c>
+      <c r="O8" t="s">
         <v>34</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>180</v>
       </c>
-      <c r="P8" s="2">
-        <v>2</v>
-      </c>
       <c r="Q8" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="S8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1008</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>7</v>
       </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
       <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
         <v>20</v>
       </c>
-      <c r="G9" s="2">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="2">
         <v>15</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0.2</v>
       </c>
       <c r="L9" s="2">
         <v>0.2</v>
       </c>
       <c r="M9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="N9" s="2">
         <v>8</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="2">
-        <v>-1</v>
-      </c>
       <c r="P9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q9" s="2">
         <v>1.8</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>4</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>1.8</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>1009</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
         <v>31</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>8</v>
       </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
       <c r="F10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
         <v>23</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>4</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="2">
-        <v>9</v>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="K10" s="2">
+        <v>9</v>
+      </c>
+      <c r="L10" s="2">
         <v>0.23</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>0.19</v>
       </c>
-      <c r="M10" s="2">
-        <v>5</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="N10" s="2">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
         <v>33</v>
       </c>
-      <c r="O10" s="2">
-        <v>-1</v>
-      </c>
       <c r="P10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q10" s="2">
         <v>1.5</v>
       </c>
-      <c r="Q10" s="2">
-        <v>2</v>
-      </c>
       <c r="R10" s="2">
+        <v>2</v>
+      </c>
+      <c r="S10" s="2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1010</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="4">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2</v>
+      <c r="E11" s="4">
+        <v>9</v>
       </c>
       <c r="F11" s="3">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3">
         <v>25</v>
       </c>
-      <c r="G11" s="3">
-        <v>5</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
+      <c r="H11" s="3">
+        <v>5</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>15</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>0.6</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>0.19</v>
       </c>
-      <c r="M11" s="3">
-        <v>3</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="N11" s="3">
+        <v>3</v>
+      </c>
+      <c r="O11" t="s">
         <v>33</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>270</v>
       </c>
-      <c r="P11" s="3">
-        <v>5</v>
-      </c>
       <c r="Q11" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R11" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="S11" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>1011</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="D12">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2">
-        <v>3</v>
+      <c r="E12">
+        <v>5</v>
       </c>
       <c r="F12" s="2">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2">
         <v>30</v>
       </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="2">
         <v>12</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>0.15</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>0.25</v>
       </c>
-      <c r="M12" s="2">
-        <v>10</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="N12" s="2">
+        <v>10</v>
+      </c>
+      <c r="O12" t="s">
         <v>33</v>
       </c>
-      <c r="O12" s="2">
-        <v>-1</v>
-      </c>
       <c r="P12" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>1012</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>6</v>
       </c>
-      <c r="E13" s="2">
-        <v>3</v>
-      </c>
       <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
         <v>33</v>
       </c>
-      <c r="G13" s="2">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="2">
+      <c r="H13" s="2">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="2">
         <v>18</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>0.11</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <v>0.3</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <v>12</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>34</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>180</v>
       </c>
-      <c r="P13" s="2">
+      <c r="Q13" s="2">
         <v>1.8</v>
       </c>
-      <c r="Q13" s="2">
-        <v>5</v>
-      </c>
       <c r="R13" s="2">
+        <v>5</v>
+      </c>
+      <c r="S13" s="2">
         <v>1.8</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1013</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
         <v>24</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>7</v>
       </c>
-      <c r="E14" s="2">
-        <v>3</v>
-      </c>
       <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2">
         <v>35</v>
       </c>
-      <c r="G14" s="2">
-        <v>3</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
+      <c r="H14" s="2">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>18</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <v>0.42</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <v>4</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>33</v>
       </c>
-      <c r="O14" s="2">
-        <v>-1</v>
-      </c>
       <c r="P14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q14" s="2">
         <v>1.5</v>
       </c>
-      <c r="Q14" s="2">
-        <v>5</v>
-      </c>
       <c r="R14" s="2">
+        <v>5</v>
+      </c>
+      <c r="S14" s="2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>1014</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>25</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>8</v>
       </c>
-      <c r="E15" s="2">
-        <v>3</v>
-      </c>
       <c r="F15" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2">
+        <v>38</v>
+      </c>
+      <c r="H15" s="2">
         <v>4</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="2">
         <v>14</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <v>0.18</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
         <v>0.26</v>
       </c>
-      <c r="M15" s="2">
-        <v>9</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="N15" s="2">
+        <v>9</v>
+      </c>
+      <c r="O15" t="s">
         <v>33</v>
       </c>
-      <c r="O15" s="2">
-        <v>-1</v>
-      </c>
       <c r="P15" s="2">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q15" s="2">
+        <v>3</v>
+      </c>
+      <c r="R15" s="2">
         <v>4</v>
       </c>
-      <c r="R15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="S15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>1015</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="4">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3">
-        <v>3</v>
+      <c r="E16" s="4">
+        <v>9</v>
       </c>
       <c r="F16" s="3">
+        <v>3</v>
+      </c>
+      <c r="G16" s="3">
         <v>40</v>
       </c>
-      <c r="G16" s="3">
-        <v>5</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="H16" s="3">
+        <v>5</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="3">
         <v>20</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>0.6</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>0.32</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>11</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="O16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>270</v>
       </c>
-      <c r="P16" s="3">
-        <v>2</v>
-      </c>
       <c r="Q16" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="S16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>1016</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2">
         <v>4</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>45</v>
       </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2">
         <v>16</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <v>0.8</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>0.35</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <v>13</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>33</v>
       </c>
-      <c r="O17" s="2">
-        <v>-1</v>
-      </c>
       <c r="P17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q17" s="2">
         <v>1.8</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="R17" s="2">
         <v>8</v>
       </c>
-      <c r="R17" s="2">
+      <c r="S17" s="2">
         <v>1.8</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>1017</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
         <v>30</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>6</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>4</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>48</v>
       </c>
-      <c r="G18" s="2">
-        <v>2</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <v>20</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>1.8</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>0.33</v>
       </c>
-      <c r="M18" s="2">
-        <v>5</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="N18" s="2">
+        <v>5</v>
+      </c>
+      <c r="O18" t="s">
         <v>34</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <v>180</v>
       </c>
-      <c r="P18" s="2">
+      <c r="Q18" s="2">
         <v>1.5</v>
       </c>
-      <c r="Q18" s="2">
-        <v>1</v>
-      </c>
       <c r="R18" s="2">
+        <v>1</v>
+      </c>
+      <c r="S18" s="2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>1018</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
         <v>31</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>7</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>4</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>50</v>
       </c>
-      <c r="G19" s="2">
-        <v>3</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="H19" s="2">
+        <v>3</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K19" s="2">
         <v>22</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>0.25</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <v>0.4</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <v>15</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>33</v>
       </c>
-      <c r="O19" s="2">
-        <v>-1</v>
-      </c>
       <c r="P19" s="2">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R19" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="S19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>1019</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
         <v>23</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>8</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="2">
         <v>4</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>53</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>4</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="2">
         <v>18</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <v>0.3</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>0.38</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <v>12</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>33</v>
       </c>
-      <c r="O20" s="2">
-        <v>-1</v>
-      </c>
       <c r="P20" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q20" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R20" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="S20" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>1020</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="4">
-        <v>9</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3">
         <v>4</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>55</v>
       </c>
-      <c r="G21" s="3">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="H21" s="3">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="3">
         <v>25</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>0.2</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>0.42</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="O21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>270</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1.8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1.8</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>1021</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
         <v>28</v>
       </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="E22">
         <v>5</v>
       </c>
       <c r="F22" s="2">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2">
         <v>60</v>
       </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="2">
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="2">
         <v>20</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="2">
         <v>0.8</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
         <v>0.45</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <v>16</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>33</v>
       </c>
-      <c r="O22" s="2">
-        <v>-1</v>
-      </c>
       <c r="P22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q22" s="2">
         <v>1.5</v>
       </c>
-      <c r="Q22" s="2">
-        <v>2</v>
-      </c>
       <c r="R22" s="2">
+        <v>2</v>
+      </c>
+      <c r="S22" s="2">
         <v>1.5</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>1022</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
         <v>24</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>6</v>
       </c>
-      <c r="E23" s="2">
-        <v>5</v>
-      </c>
       <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2">
         <v>63</v>
       </c>
-      <c r="G23" s="2">
-        <v>2</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2" t="s">
+      <c r="H23" s="2">
+        <v>2</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <v>25</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <v>0.2</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <v>0.43</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <v>6</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>34</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <v>180</v>
       </c>
-      <c r="P23" s="2">
-        <v>3</v>
-      </c>
       <c r="Q23" s="2">
+        <v>3</v>
+      </c>
+      <c r="R23" s="2">
         <v>8</v>
       </c>
-      <c r="R23" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>1023</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
         <v>25</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>7</v>
       </c>
-      <c r="E24" s="2">
-        <v>5</v>
-      </c>
       <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2">
         <v>65</v>
       </c>
-      <c r="G24" s="2">
-        <v>3</v>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" s="2">
+      <c r="H24" s="2">
+        <v>3</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="2">
         <v>30</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <v>0.23</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <v>0.5</v>
       </c>
-      <c r="M24" s="2">
+      <c r="N24" s="2">
         <v>18</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="2">
-        <v>-1</v>
-      </c>
       <c r="P24" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>1024</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
         <v>27</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>8</v>
       </c>
-      <c r="E25" s="2">
-        <v>5</v>
-      </c>
       <c r="F25" s="2">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2">
         <v>68</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="2">
         <v>4</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="I25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="2">
         <v>24</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <v>0.6</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
         <v>0.48</v>
       </c>
-      <c r="M25" s="2">
+      <c r="N25" s="2">
         <v>15</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>33</v>
       </c>
-      <c r="O25" s="2">
-        <v>-1</v>
-      </c>
       <c r="P25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q25" s="2">
         <v>1.8</v>
       </c>
-      <c r="Q25" s="2">
-        <v>5</v>
-      </c>
       <c r="R25" s="2">
+        <v>5</v>
+      </c>
+      <c r="S25" s="2">
         <v>1.8</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>1025</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="4">
-        <v>9</v>
-      </c>
-      <c r="E26" s="3">
-        <v>5</v>
+      <c r="E26" s="4">
+        <v>9</v>
       </c>
       <c r="F26" s="3">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
         <v>70</v>
       </c>
-      <c r="G26" s="3">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="H26" s="3">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="3">
         <v>35</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>0.15</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="O26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>270</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1.5</v>
       </c>
-      <c r="Q26" s="3">
-        <v>1</v>
-      </c>
       <c r="R26" s="3">
+        <v>1</v>
+      </c>
+      <c r="S26" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>2001</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
       <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
         <v>0</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="2">
-        <v>-1</v>
-      </c>
       <c r="K27" s="2">
         <v>-1</v>
       </c>
@@ -2001,33 +2119,36 @@
       <c r="R27" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S27" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>2002</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="2">
-        <v>2</v>
-      </c>
       <c r="F28" s="2">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="2">
-        <v>-1</v>
-      </c>
       <c r="K28" s="2">
         <v>-1</v>
       </c>
@@ -2052,33 +2173,36 @@
       <c r="R28" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S28" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>2003</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="2">
-        <v>3</v>
-      </c>
       <c r="F29" s="2">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2">
         <v>0</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J29" s="2">
-        <v>-1</v>
-      </c>
       <c r="K29" s="2">
         <v>-1</v>
       </c>
@@ -2103,33 +2227,36 @@
       <c r="R29" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S29" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>2004</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="2">
         <v>4</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J30" s="2">
-        <v>-1</v>
-      </c>
       <c r="K30" s="2">
         <v>-1</v>
       </c>
@@ -2154,33 +2281,36 @@
       <c r="R30" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S30" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>2005</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="2">
-        <v>5</v>
-      </c>
       <c r="F31" s="2">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2">
         <v>0</v>
       </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J31" s="2">
-        <v>-1</v>
-      </c>
       <c r="K31" s="2">
         <v>-1</v>
       </c>
@@ -2205,9 +2335,465 @@
       <c r="R31" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="I32" s="2"/>
+      <c r="S31" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>5001</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="6">
+        <v>5</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="5">
+        <v>5</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="N32" s="5">
+        <v>3</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P32" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="R32" s="5">
+        <v>5</v>
+      </c>
+      <c r="S32" s="5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>5002</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="6">
+        <v>10</v>
+      </c>
+      <c r="F33" s="5">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5">
+        <v>3</v>
+      </c>
+      <c r="H33" s="5">
+        <v>2</v>
+      </c>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" s="5">
+        <v>2</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="N33" s="5">
+        <v>1</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="5">
+        <v>180</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>5</v>
+      </c>
+      <c r="R33" s="5">
+        <v>1</v>
+      </c>
+      <c r="S33" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>5003</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="6">
+        <v>7</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5">
+        <v>5</v>
+      </c>
+      <c r="H34" s="5">
+        <v>3</v>
+      </c>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="5">
+        <v>10</v>
+      </c>
+      <c r="L34" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="N34" s="5">
+        <v>1</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P34" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>2</v>
+      </c>
+      <c r="R34" s="5">
+        <v>2</v>
+      </c>
+      <c r="S34" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>5004</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="6">
+        <v>8</v>
+      </c>
+      <c r="F35" s="5">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5">
+        <v>8</v>
+      </c>
+      <c r="H35" s="5">
+        <v>4</v>
+      </c>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="5">
+        <v>6</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="M35" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="N35" s="5">
+        <v>4</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P35" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="R35" s="5">
+        <v>8</v>
+      </c>
+      <c r="S35" s="5">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>5005</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="6">
+        <v>9</v>
+      </c>
+      <c r="F36" s="5">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5">
+        <v>10</v>
+      </c>
+      <c r="H36" s="5">
+        <v>5</v>
+      </c>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" s="5">
+        <v>12</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="N36" s="5">
+        <v>6</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P36" s="5">
+        <v>270</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>3</v>
+      </c>
+      <c r="R36" s="5">
+        <v>10</v>
+      </c>
+      <c r="S36" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>5006</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="6">
+        <v>5</v>
+      </c>
+      <c r="F37" s="5">
+        <v>2</v>
+      </c>
+      <c r="G37" s="5">
+        <v>15</v>
+      </c>
+      <c r="H37" s="5">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K37" s="5">
+        <v>10</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="N37" s="5">
+        <v>7</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P37" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>3</v>
+      </c>
+      <c r="R37" s="5">
+        <v>5</v>
+      </c>
+      <c r="S37" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>5007</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="6">
+        <v>6</v>
+      </c>
+      <c r="F38" s="5">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5">
+        <v>18</v>
+      </c>
+      <c r="H38" s="5">
+        <v>2</v>
+      </c>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" s="5">
+        <v>12</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="N38" s="5">
+        <v>2</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="5">
+        <v>180</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>2</v>
+      </c>
+      <c r="R38" s="5">
+        <v>5</v>
+      </c>
+      <c r="S38" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>5008</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="6">
+        <v>7</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5">
+        <v>20</v>
+      </c>
+      <c r="H39" s="5">
+        <v>3</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K39" s="5">
+        <v>15</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="N39" s="5">
+        <v>8</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="R39" s="5">
+        <v>4</v>
+      </c>
+      <c r="S39" s="5">
+        <v>1.8</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
